--- a/template/Packaging_Template.xlsx
+++ b/template/Packaging_Template.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Packaging Name</t>
+  </si>
+  <si>
+    <t>Packaging Type</t>
   </si>
 </sst>
 </file>
@@ -42,16 +45,8 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+  <fonts count="21">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -529,140 +524,139 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -998,16 +992,23 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"Original,Repack"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>

--- a/template/Packaging_Template.xlsx
+++ b/template/Packaging_Template.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Packaging Name</t>
   </si>
   <si>
     <t>Packaging Type</t>
+  </si>
+  <si>
+    <t>By Weight</t>
   </si>
 </sst>
 </file>
@@ -995,7 +998,9 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1004,9 +1009,12 @@
       <c r="I1" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>"Original,Repack"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
